--- a/Pruebas calificadas/COLEGIO-DELIA-ZAPATA-OLIVELLA-(IED)PRUEBA-DIAGNÓSTICA-705_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-DELIA-ZAPATA-OLIVELLA-(IED)PRUEBA-DIAGNÓSTICA-705_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1562,11 +1550,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -1574,7 +1558,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1815,11 +1799,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -1827,7 +1807,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2064,11 +2044,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -2076,7 +2052,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2309,11 +2285,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -2321,7 +2293,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2562,11 +2534,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -2574,7 +2542,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2815,11 +2783,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -2827,7 +2791,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3064,11 +3028,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -3076,7 +3036,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3313,11 +3273,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -3325,7 +3281,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3566,11 +3522,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -3578,7 +3530,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3819,11 +3771,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -3831,7 +3779,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4072,11 +4020,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -4084,7 +4028,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4325,11 +4269,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -4337,7 +4277,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4578,11 +4518,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -4590,7 +4526,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4831,11 +4767,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -4843,7 +4775,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5084,11 +5016,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -5096,7 +5024,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5337,11 +5265,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -5349,7 +5273,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5590,11 +5514,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -5602,7 +5522,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5843,11 +5763,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -5855,7 +5771,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6096,11 +6012,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -6108,7 +6020,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6349,11 +6261,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -6361,7 +6269,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6602,11 +6510,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -6614,7 +6518,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6855,11 +6759,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -6867,7 +6767,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7108,11 +7008,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -7120,7 +7016,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7361,11 +7257,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -7373,7 +7265,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7610,11 +7502,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -7622,7 +7510,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7863,11 +7751,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -7875,7 +7759,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8116,11 +8000,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -8128,7 +8008,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8365,11 +8245,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -8377,7 +8253,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8618,11 +8494,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -8630,7 +8502,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8871,11 +8743,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -8883,7 +8751,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9120,11 +8988,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -9132,7 +8996,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9373,11 +9237,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -9385,7 +9245,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9626,11 +9486,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -9638,7 +9494,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9879,11 +9735,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -9891,7 +9743,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10128,11 +9980,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -10140,7 +9988,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10373,11 +10221,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -10385,7 +10229,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10590,11 +10434,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -10602,7 +10442,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10831,11 +10671,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -10843,7 +10679,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11048,11 +10884,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -11060,7 +10892,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11289,11 +11121,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -11301,7 +11129,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11522,11 +11350,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -11534,7 +11358,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11775,11 +11599,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -11787,7 +11607,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12028,11 +11848,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -12040,7 +11856,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12281,11 +12097,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -12293,7 +12105,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12534,11 +12346,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -12546,7 +12354,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12787,11 +12595,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -12799,7 +12603,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13040,11 +12844,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -13052,7 +12852,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13293,11 +13093,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -13305,7 +13101,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13546,11 +13342,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -13558,7 +13350,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13799,11 +13591,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -13811,7 +13599,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14052,11 +13840,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -14064,7 +13848,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14305,11 +14089,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -14317,7 +14097,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14558,11 +14338,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -14570,7 +14346,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14811,11 +14587,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -14823,7 +14595,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15064,11 +14836,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -15076,7 +14844,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15317,11 +15085,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -15329,7 +15093,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15570,11 +15334,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -15582,7 +15342,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15823,11 +15583,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -15835,7 +15591,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16052,11 +15808,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -16064,7 +15816,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16305,11 +16057,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -16317,7 +16065,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16558,11 +16306,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -16570,7 +16314,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16811,11 +16555,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -16823,7 +16563,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17064,11 +16804,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -17076,7 +16812,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17317,11 +17053,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -17329,7 +17061,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17570,11 +17302,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -17582,7 +17310,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
